--- a/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
+++ b/content/Value Investing/Zegona Communications Plc - ZEG/Precio_Accion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\palfa\Documents\GitHub\palfaros-knowledge-base\content\Value Investing\Zegona Communications Plc - ZEG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEE3FB3-FE58-4C0B-BE6A-53B870C366A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCC99C3-3053-4CB9-B3C3-BDA6E6D4A5EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="8" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="8" activeTab="8" xr2:uid="{BFFC155E-449D-4069-884C-DE4A947B6688}"/>
   </bookViews>
   <sheets>
     <sheet name="Dividendo parcial + Preferentes" sheetId="2" r:id="rId1"/>
@@ -8649,14 +8649,13 @@
         <v>1250</v>
       </c>
       <c r="C11" s="7">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="D11" s="7">
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="E11" s="7">
-        <f t="shared" ref="E11" si="2">D11</f>
-        <v>0</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="12" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -8686,15 +8685,15 @@
       </c>
       <c r="C13" s="9">
         <f>C11-C12</f>
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="D13" s="9">
         <f>D11-D12</f>
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="E13" s="9">
         <f>E11-E12</f>
-        <v>0</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="14" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -8727,16 +8726,16 @@
         <v>62.5</v>
       </c>
       <c r="C15" s="2">
-        <f t="shared" ref="C15:E15" si="3">C14*C13</f>
-        <v>0</v>
+        <f t="shared" ref="C15:E15" si="2">C14*C13</f>
+        <v>62.5</v>
       </c>
       <c r="D15" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>62.5</v>
       </c>
       <c r="E15" s="2">
-        <f t="shared" si="3"/>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>62.5</v>
       </c>
     </row>
     <row r="16" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -8760,11 +8759,11 @@
         <v>3640</v>
       </c>
       <c r="D17" s="9">
-        <f t="shared" ref="D17:E17" si="4">C17</f>
+        <f t="shared" ref="D17:E17" si="3">C17</f>
         <v>3640</v>
       </c>
       <c r="E17" s="9">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>3640</v>
       </c>
     </row>
@@ -8777,15 +8776,15 @@
         <v>0.17499999999999999</v>
       </c>
       <c r="C18" s="8">
-        <f t="shared" ref="C18:E18" si="5">17.5%</f>
+        <f t="shared" ref="C18:E18" si="4">17.5%</f>
         <v>0.17499999999999999</v>
       </c>
       <c r="D18" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.17499999999999999</v>
       </c>
       <c r="E18" s="8">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>0.17499999999999999</v>
       </c>
     </row>
@@ -8798,15 +8797,15 @@
         <v>637</v>
       </c>
       <c r="C19">
-        <f t="shared" ref="C19:E19" si="6">C18*C17</f>
+        <f t="shared" ref="C19:E19" si="5">C18*C17</f>
         <v>637</v>
       </c>
       <c r="D19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>637</v>
       </c>
       <c r="E19">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>637</v>
       </c>
     </row>
@@ -8820,15 +8819,15 @@
       </c>
       <c r="C20" s="2">
         <f>C9+C15+C19</f>
-        <v>4128</v>
+        <v>4190.5</v>
       </c>
       <c r="D20" s="2">
         <f>D9+D15+D19</f>
-        <v>5469</v>
+        <v>5531.5</v>
       </c>
       <c r="E20" s="2">
         <f>E9+E15+E19</f>
-        <v>6810</v>
+        <v>6872.5</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -8840,15 +8839,15 @@
         <v>225.71380199999999</v>
       </c>
       <c r="C21" s="2">
-        <f t="shared" ref="C21:E21" si="7">225713802/1000000</f>
+        <f t="shared" ref="C21:E21" si="6">225713802/1000000</f>
         <v>225.71380199999999</v>
       </c>
       <c r="D21" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>225.71380199999999</v>
       </c>
       <c r="E21" s="2">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>225.71380199999999</v>
       </c>
     </row>
@@ -8862,15 +8861,15 @@
       </c>
       <c r="C22" s="1">
         <f>C20/C21</f>
-        <v>18.288646788201284</v>
+        <v>18.565546115784272</v>
       </c>
       <c r="D22" s="1">
         <f>D20/D21</f>
-        <v>24.229798760821904</v>
+        <v>24.506698088404892</v>
       </c>
       <c r="E22" s="1">
         <f>E20/E21</f>
-        <v>30.170950733442524</v>
+        <v>30.447850061025513</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
@@ -8882,15 +8881,15 @@
         <v>1.17</v>
       </c>
       <c r="C23">
-        <f t="shared" ref="C23:E23" si="8">1.17</f>
+        <f t="shared" ref="C23:E23" si="7">1.17</f>
         <v>1.17</v>
       </c>
       <c r="D23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.17</v>
       </c>
       <c r="E23">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>1.17</v>
       </c>
     </row>
@@ -8903,16 +8902,16 @@
         <v>10.790080464242438</v>
       </c>
       <c r="C24" s="1">
-        <f t="shared" ref="C24:E24" si="9">C22/C23</f>
-        <v>15.631322041197679</v>
+        <f t="shared" ref="C24:E24" si="8">C22/C23</f>
+        <v>15.867988133148952</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" si="9"/>
-        <v>20.709229710104193</v>
+        <f t="shared" si="8"/>
+        <v>20.945895802055464</v>
       </c>
       <c r="E24" s="1">
-        <f t="shared" si="9"/>
-        <v>25.787137379010705</v>
+        <f t="shared" si="8"/>
+        <v>26.02380347096198</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -8924,16 +8923,16 @@
         <v>1079.0080464242437</v>
       </c>
       <c r="C25" s="2">
-        <f t="shared" ref="C25:E25" si="10">C24*100</f>
-        <v>1563.1322041197679</v>
+        <f t="shared" ref="C25:E25" si="9">C24*100</f>
+        <v>1586.7988133148951</v>
       </c>
       <c r="D25" s="2">
-        <f t="shared" si="10"/>
-        <v>2070.9229710104191</v>
+        <f t="shared" si="9"/>
+        <v>2094.5895802055466</v>
       </c>
       <c r="E25" s="2">
-        <f t="shared" si="10"/>
-        <v>2578.7137379010705</v>
+        <f t="shared" si="9"/>
+        <v>2602.380347096198</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -8966,16 +8965,16 @@
         <v>0.81345890155335088</v>
       </c>
       <c r="C27" s="3">
-        <f t="shared" ref="C27:E27" si="11">C25/C26-1</f>
-        <v>1.6271129481004505</v>
+        <f t="shared" ref="C27:E27" si="10">C25/C26-1</f>
+        <v>1.6668887618737736</v>
       </c>
       <c r="D27" s="3">
-        <f t="shared" si="11"/>
-        <v>2.4805428084208727</v>
+        <f t="shared" si="10"/>
+        <v>2.5203186221941958</v>
       </c>
       <c r="E27" s="3">
-        <f t="shared" si="11"/>
-        <v>3.3339726687412954</v>
+        <f t="shared" si="10"/>
+        <v>3.3737484825146185</v>
       </c>
     </row>
   </sheetData>
